--- a/artfynd/A 50983-2024 artfynd.xlsx
+++ b/artfynd/A 50983-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66547883</v>
+        <v>66547732</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540154.2074307024</v>
+        <v>540189</v>
       </c>
       <c r="R2" t="n">
-        <v>7263268.759172551</v>
+        <v>7263192</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>26354</t>
+          <t>26229</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66547879</v>
+        <v>66547726</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540070.5115209778</v>
+        <v>540180</v>
       </c>
       <c r="R3" t="n">
-        <v>7263336.565635735</v>
+        <v>7263228</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +861,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -902,22 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66547880</v>
+        <v>66547835</v>
       </c>
       <c r="B4" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,17 +907,21 @@
           <t>(Fr.) Krieglst.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540241.5035821543</v>
+        <v>540146</v>
       </c>
       <c r="R4" t="n">
-        <v>7263241.714625816</v>
+        <v>7263347</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,21 +951,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,7 +967,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>26313</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1019,22 +978,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66547885</v>
+        <v>66547852</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +996,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540111.183703172</v>
+        <v>540011</v>
       </c>
       <c r="R5" t="n">
-        <v>7263282.290905532</v>
+        <v>7263248</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,21 +1053,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1069,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>26328</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1136,22 +1080,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66547900</v>
+        <v>66547878</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539993.7686621943</v>
+        <v>540071</v>
       </c>
       <c r="R6" t="n">
-        <v>7263382.867518048</v>
+        <v>7263337</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,21 +1155,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1171,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>26369</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1253,22 +1182,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66547731</v>
+        <v>66547880</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,21 +1200,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540189.3640534286</v>
+        <v>540242</v>
       </c>
       <c r="R7" t="n">
-        <v>7263192.390651815</v>
+        <v>7263242</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1330,22 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,7 +1273,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>26351</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1370,22 +1284,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66547727</v>
+        <v>66547881</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,38 +1302,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540179.7234010847</v>
+        <v>540259</v>
       </c>
       <c r="R8" t="n">
-        <v>7263227.984279819</v>
+        <v>7263225</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1451,22 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,7 +1375,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>26225</t>
+          <t>26352</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1491,44 +1386,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66547884</v>
+        <v>66547888</v>
       </c>
       <c r="B9" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540154.2074307024</v>
+        <v>540014</v>
       </c>
       <c r="R9" t="n">
-        <v>7263268.759172551</v>
+        <v>7263290</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1571,21 +1461,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1597,7 +1477,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26359</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1615,15 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66547834</v>
+        <v>66547890</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,38 +1506,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540146.4788159684</v>
+        <v>539982</v>
       </c>
       <c r="R10" t="n">
-        <v>7263346.749946395</v>
+        <v>7263271</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1692,21 +1563,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1718,7 +1579,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>26361</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1736,37 +1597,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66547881</v>
+        <v>66547846</v>
       </c>
       <c r="B11" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1776,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540258.7818000455</v>
+        <v>540137</v>
       </c>
       <c r="R11" t="n">
-        <v>7263225.336346947</v>
+        <v>7263212</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1809,21 +1665,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1835,7 +1681,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1853,54 +1699,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66547720</v>
+        <v>66547850</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540293.8498215334</v>
+        <v>540047</v>
       </c>
       <c r="R12" t="n">
-        <v>7263155.613565125</v>
+        <v>7263262</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1927,22 +1764,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,7 +1783,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1967,44 +1794,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66547730</v>
+        <v>66547731</v>
       </c>
       <c r="B13" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2014,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540189.3640534286</v>
+        <v>540189</v>
       </c>
       <c r="R13" t="n">
-        <v>7263192.390651815</v>
+        <v>7263192</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2047,21 +1869,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2073,7 +1885,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2091,15 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66547736</v>
+        <v>66547837</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,38 +1914,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540355.4646050897</v>
+        <v>540146</v>
       </c>
       <c r="R14" t="n">
-        <v>7263091.242203163</v>
+        <v>7263347</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2168,21 +1971,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +1987,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>26315</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2212,15 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66547840</v>
+        <v>66547833</v>
       </c>
       <c r="B15" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540114.6232050281</v>
+        <v>540146</v>
       </c>
       <c r="R15" t="n">
-        <v>7263183.46796721</v>
+        <v>7263347</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2285,21 +2073,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2311,7 +2089,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>26311</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2322,22 +2100,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66547738</v>
+        <v>66547841</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,21 +2118,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2369,10 +2142,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540372.4452051978</v>
+        <v>540115</v>
       </c>
       <c r="R16" t="n">
-        <v>7263096.462642422</v>
+        <v>7263183</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2402,21 +2175,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2428,7 +2191,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2439,22 +2202,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66547886</v>
+        <v>66547843</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2462,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2486,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540029.0452107345</v>
+        <v>540140</v>
       </c>
       <c r="R17" t="n">
-        <v>7263297.362815768</v>
+        <v>7263215</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2519,21 +2277,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2545,7 +2293,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2556,22 +2304,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66547838</v>
+        <v>66547847</v>
       </c>
       <c r="B18" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,10 +2346,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540146.4788159684</v>
+        <v>540104</v>
       </c>
       <c r="R18" t="n">
-        <v>7263346.749946395</v>
+        <v>7263245</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2636,21 +2379,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2662,7 +2395,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2673,22 +2406,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>66547734</v>
+        <v>66547882</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2696,38 +2424,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540200.2719529908</v>
+        <v>540131</v>
       </c>
       <c r="R19" t="n">
-        <v>7263125.241051289</v>
+        <v>7263211</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2754,22 +2478,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2783,7 +2497,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2801,15 +2515,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66547882</v>
+        <v>66547901</v>
       </c>
       <c r="B20" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,10 +2550,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540130.8847643629</v>
+        <v>540131</v>
       </c>
       <c r="R20" t="n">
-        <v>7263210.694526652</v>
+        <v>7263364</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2874,21 +2583,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2900,7 +2599,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2918,37 +2617,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>66547852</v>
+        <v>66547730</v>
       </c>
       <c r="B21" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2958,10 +2652,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540010.5904606235</v>
+        <v>540189</v>
       </c>
       <c r="R21" t="n">
-        <v>7263248.090430467</v>
+        <v>7263192</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2988,22 +2682,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3017,7 +2701,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>26328</t>
+          <t>26227</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3028,44 +2712,39 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>66547843</v>
+        <v>66547849</v>
       </c>
       <c r="B22" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3075,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540139.9814939728</v>
+        <v>540094</v>
       </c>
       <c r="R22" t="n">
-        <v>7263214.558602282</v>
+        <v>7263261</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3108,21 +2787,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3134,7 +2803,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>26320</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3152,50 +2821,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66547828</v>
+        <v>66547719</v>
       </c>
       <c r="B23" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540175.3650992169</v>
+        <v>540289</v>
       </c>
       <c r="R23" t="n">
-        <v>7263483.813131652</v>
+        <v>7263111</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3222,22 +2890,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,7 +2909,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>26217</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3269,50 +2927,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>66547732</v>
+        <v>66547720</v>
       </c>
       <c r="B24" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540189.3640534286</v>
+        <v>540294</v>
       </c>
       <c r="R24" t="n">
-        <v>7263192.390651815</v>
+        <v>7263156</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3342,21 +2999,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3368,7 +3015,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>26229</t>
+          <t>26218</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3386,50 +3033,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>66547845</v>
+        <v>66547722</v>
       </c>
       <c r="B25" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540128.0025611944</v>
+        <v>540236</v>
       </c>
       <c r="R25" t="n">
-        <v>7263208.577722815</v>
+        <v>7263225</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3456,22 +3102,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3485,7 +3121,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>26220</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3496,57 +3132,56 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>66547839</v>
+        <v>66547725</v>
       </c>
       <c r="B26" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540146.4788159684</v>
+        <v>540206</v>
       </c>
       <c r="R26" t="n">
-        <v>7263346.749946395</v>
+        <v>7263225</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3573,22 +3208,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3602,7 +3227,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>26317</t>
+          <t>26223</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3620,19 +3245,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>66547725</v>
+        <v>66547727</v>
       </c>
       <c r="B27" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3655,7 +3275,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3664,10 +3284,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540205.9604889299</v>
+        <v>540180</v>
       </c>
       <c r="R27" t="n">
-        <v>7263225.43811141</v>
+        <v>7263228</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3697,21 +3317,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3723,7 +3333,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3741,50 +3351,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>66547889</v>
+        <v>66547728</v>
       </c>
       <c r="B28" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>539982.4170175472</v>
+        <v>540189</v>
       </c>
       <c r="R28" t="n">
-        <v>7263270.551770543</v>
+        <v>7263192</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3811,22 +3420,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3840,7 +3439,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>26360</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3858,50 +3457,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>66547878</v>
+        <v>66547734</v>
       </c>
       <c r="B29" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540070.5115209778</v>
+        <v>540200</v>
       </c>
       <c r="R29" t="n">
-        <v>7263336.565635735</v>
+        <v>7263125</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3928,22 +3526,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3957,7 +3545,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3968,57 +3556,56 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>66547737</v>
+        <v>66547736</v>
       </c>
       <c r="B30" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540355.4646050897</v>
+        <v>540355</v>
       </c>
       <c r="R30" t="n">
-        <v>7263091.242203163</v>
+        <v>7263091</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -4048,21 +3635,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4074,7 +3651,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>26232</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4092,50 +3669,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>66547718</v>
+        <v>66547739</v>
       </c>
       <c r="B31" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540289.4798184499</v>
+        <v>540372</v>
       </c>
       <c r="R31" t="n">
-        <v>7263110.68604412</v>
+        <v>7263096</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4162,22 +3738,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4191,7 +3757,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>26216</t>
+          <t>26234</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4209,50 +3775,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>66547888</v>
+        <v>66547829</v>
       </c>
       <c r="B32" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540014.1727941483</v>
+        <v>540175</v>
       </c>
       <c r="R32" t="n">
-        <v>7263290.096595969</v>
+        <v>7263484</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4282,21 +3847,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4308,7 +3863,7 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>26359</t>
+          <t>26307</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4326,42 +3881,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>66547835</v>
+        <v>66547834</v>
       </c>
       <c r="B33" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4370,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540146.4788159684</v>
+        <v>540146</v>
       </c>
       <c r="R33" t="n">
-        <v>7263346.749946395</v>
+        <v>7263347</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4403,21 +3953,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4429,7 +3969,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>26313</t>
+          <t>26312</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4447,19 +3987,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>66547887</v>
+        <v>66547840</v>
       </c>
       <c r="B34" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4487,10 +4022,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540014.1727941483</v>
+        <v>540115</v>
       </c>
       <c r="R34" t="n">
-        <v>7263290.096595969</v>
+        <v>7263183</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4520,21 +4055,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4546,7 +4071,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>26358</t>
+          <t>26318</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4557,26 +4082,21 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>66547739</v>
+        <v>66547886</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4597,21 +4117,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540372.4452051978</v>
+        <v>540029</v>
       </c>
       <c r="R35" t="n">
-        <v>7263096.462642422</v>
+        <v>7263297</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4641,21 +4157,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4667,7 +4173,7 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>26234</t>
+          <t>26357</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4685,37 +4191,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>66547721</v>
+        <v>66547887</v>
       </c>
       <c r="B36" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4725,10 +4226,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540293.8498215334</v>
+        <v>540014</v>
       </c>
       <c r="R36" t="n">
-        <v>7263155.613565125</v>
+        <v>7263290</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4755,22 +4256,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4784,7 +4275,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>26219</t>
+          <t>26358</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4802,37 +4293,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>66547849</v>
+        <v>66547903</v>
       </c>
       <c r="B37" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4842,10 +4328,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540093.5949243368</v>
+        <v>540187</v>
       </c>
       <c r="R37" t="n">
-        <v>7263260.86270697</v>
+        <v>7263331</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4875,21 +4361,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4901,7 +4377,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>26325</t>
+          <t>26372</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4912,22 +4388,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>66547902</v>
+        <v>66547724</v>
       </c>
       <c r="B38" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4935,21 +4406,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4959,10 +4430,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540131.2638218725</v>
+        <v>540206</v>
       </c>
       <c r="R38" t="n">
-        <v>7263364.402785186</v>
+        <v>7263225</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4989,22 +4460,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5018,7 +4479,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>26371</t>
+          <t>26222</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5036,15 +4497,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>66547827</v>
+        <v>66547884</v>
       </c>
       <c r="B39" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5052,21 +4508,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6439</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5076,10 +4532,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>540175.3650992169</v>
+        <v>540154</v>
       </c>
       <c r="R39" t="n">
-        <v>7263483.813131652</v>
+        <v>7263269</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -5109,21 +4565,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5135,7 +4581,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>26305</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5153,37 +4599,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>66547846</v>
+        <v>66547827</v>
       </c>
       <c r="B40" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1204</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5193,10 +4634,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>540137.1107397681</v>
+        <v>540175</v>
       </c>
       <c r="R40" t="n">
-        <v>7263211.611100825</v>
+        <v>7263484</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5226,21 +4667,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5252,7 +4683,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>26305</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5263,44 +4694,39 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>66547901</v>
+        <v>66547845</v>
       </c>
       <c r="B41" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5310,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>540131.2638218725</v>
+        <v>540128</v>
       </c>
       <c r="R41" t="n">
-        <v>7263364.402785186</v>
+        <v>7263209</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5343,21 +4769,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5369,7 +4785,7 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>26370</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5380,44 +4796,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>66547723</v>
+        <v>66547828</v>
       </c>
       <c r="B42" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5427,10 +4838,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>540235.9113926201</v>
+        <v>540175</v>
       </c>
       <c r="R42" t="n">
-        <v>7263225.020554107</v>
+        <v>7263484</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5457,22 +4868,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5486,7 +4887,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>26221</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5504,37 +4905,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>66547850</v>
+        <v>66547839</v>
       </c>
       <c r="B43" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5544,10 +4940,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>540046.5786787429</v>
+        <v>540146</v>
       </c>
       <c r="R43" t="n">
-        <v>7263262.293444882</v>
+        <v>7263347</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5577,21 +4973,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5603,7 +4989,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>26326</t>
+          <t>26317</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5614,44 +5000,39 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>66547825</v>
+        <v>66547848</v>
       </c>
       <c r="B44" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5661,10 +5042,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>540175.3650992169</v>
+        <v>540104</v>
       </c>
       <c r="R44" t="n">
-        <v>7263483.813131652</v>
+        <v>7263245</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5694,21 +5075,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5720,7 +5091,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>26304</t>
+          <t>26324</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5731,61 +5102,52 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>66547719</v>
+        <v>66547902</v>
       </c>
       <c r="B45" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>540289.4798184499</v>
+        <v>540131</v>
       </c>
       <c r="R45" t="n">
-        <v>7263110.68604412</v>
+        <v>7263364</v>
       </c>
       <c r="S45" t="n">
         <v>50</v>
@@ -5812,22 +5174,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5841,7 +5193,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>26217</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5859,15 +5211,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>66547728</v>
+        <v>66547718</v>
       </c>
       <c r="B46" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5875,38 +5222,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>540189.3640534286</v>
+        <v>540289</v>
       </c>
       <c r="R46" t="n">
-        <v>7263192.390651815</v>
+        <v>7263111</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5936,21 +5279,11 @@
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2014-09-07</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5962,7 +5295,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>26216</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5980,15 +5313,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>66547903</v>
+        <v>66547721</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5996,21 +5324,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6020,10 +5348,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>540186.6197307439</v>
+        <v>540294</v>
       </c>
       <c r="R47" t="n">
-        <v>7263331.102270099</v>
+        <v>7263156</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -6050,22 +5378,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6079,7 +5397,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>26372</t>
+          <t>26219</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6097,15 +5415,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>66547837</v>
+        <v>66547723</v>
       </c>
       <c r="B48" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6113,21 +5426,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6137,10 +5450,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>540146.4788159684</v>
+        <v>540236</v>
       </c>
       <c r="R48" t="n">
-        <v>7263346.749946395</v>
+        <v>7263225</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -6167,22 +5480,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6196,7 +5499,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>26315</t>
+          <t>26221</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6214,37 +5517,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>66547724</v>
+        <v>66547737</v>
       </c>
       <c r="B49" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6254,10 +5552,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>540205.9604889299</v>
+        <v>540355</v>
       </c>
       <c r="R49" t="n">
-        <v>7263225.43811141</v>
+        <v>7263091</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6284,22 +5582,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6313,7 +5601,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>26222</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6331,15 +5619,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>66547829</v>
+        <v>66547825</v>
       </c>
       <c r="B50" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6347,38 +5630,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Forsmarkskogen, Ly lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>540175.3650992169</v>
+        <v>540175</v>
       </c>
       <c r="R50" t="n">
-        <v>7263483.813131652</v>
+        <v>7263484</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6408,21 +5687,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6434,7 +5703,7 @@
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>26304</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6452,15 +5721,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>66547877</v>
+        <v>66547879</v>
       </c>
       <c r="B51" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6468,21 +5732,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6492,10 +5756,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>540012.4565706467</v>
+        <v>540071</v>
       </c>
       <c r="R51" t="n">
-        <v>7263415.109598515</v>
+        <v>7263337</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6525,21 +5789,11 @@
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2014-09-08</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6551,7 +5805,7 @@
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>26350</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6566,712 +5820,6 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>66547841</v>
-      </c>
-      <c r="B52" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Forsmarkskogen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>540114.6232050281</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7263183.46796721</v>
-      </c>
-      <c r="S52" t="n">
-        <v>50</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>26319</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>66547848</v>
-      </c>
-      <c r="B53" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Forsmarkskogen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>540103.7917684797</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7263245.217087183</v>
-      </c>
-      <c r="S53" t="n">
-        <v>50</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>26324</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>66547890</v>
-      </c>
-      <c r="B54" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Forsmarkskogen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>539982.4170175472</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7263270.551770543</v>
-      </c>
-      <c r="S54" t="n">
-        <v>50</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>26361</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>66547726</v>
-      </c>
-      <c r="B55" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Forsmarkskogen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>540179.7234010847</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7263227.984279819</v>
-      </c>
-      <c r="S55" t="n">
-        <v>50</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>26224</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>66547722</v>
-      </c>
-      <c r="B56" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Forsmarkskogen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>540235.9113926201</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7263225.020554107</v>
-      </c>
-      <c r="S56" t="n">
-        <v>50</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2014-09-07</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>26220</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Via Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>66547847</v>
-      </c>
-      <c r="B57" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Forsmarkskogen, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>540103.7917684797</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7263245.217087183</v>
-      </c>
-      <c r="S57" t="n">
-        <v>50</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2014-09-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>26323</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Malin Sahlin</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
